--- a/backend/data/financials_by_company/1818.HK.xlsx
+++ b/backend/data/financials_by_company/1818.HK.xlsx
@@ -667,202 +667,202 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-76839437.01971599</v>
+        <v>-147835674</v>
       </c>
       <c r="C2" t="n">
-        <v>0.169392</v>
+        <v>0.322</v>
       </c>
       <c r="D2" t="n">
-        <v>4480201000</v>
+        <v>2223160000</v>
       </c>
       <c r="E2" t="n">
-        <v>-453620000</v>
+        <v>-459117000</v>
       </c>
       <c r="F2" t="n">
-        <v>-453620000</v>
+        <v>-459117000</v>
       </c>
       <c r="G2" t="n">
-        <v>1450799000</v>
+        <v>33697000</v>
       </c>
       <c r="H2" t="n">
-        <v>1348894000</v>
+        <v>874493000</v>
       </c>
       <c r="I2" t="n">
-        <v>7028727000</v>
+        <v>4167369000</v>
       </c>
       <c r="J2" t="n">
-        <v>4026581000</v>
+        <v>1764043000</v>
       </c>
       <c r="K2" t="n">
-        <v>2677687000</v>
+        <v>889550000</v>
       </c>
       <c r="L2" t="n">
-        <v>-343856000</v>
+        <v>-427230000</v>
       </c>
       <c r="M2" t="n">
-        <v>448799000</v>
+        <v>607867000</v>
       </c>
       <c r="N2" t="n">
-        <v>200738000</v>
+        <v>180637000</v>
       </c>
       <c r="O2" t="n">
-        <v>1827579562.980284</v>
+        <v>344978326</v>
       </c>
       <c r="P2" t="n">
-        <v>1450799000</v>
+        <v>33697000</v>
       </c>
       <c r="Q2" t="n">
-        <v>8515884000</v>
+        <v>5651499000</v>
       </c>
       <c r="R2" t="n">
-        <v>3361639000</v>
+        <v>3270393000</v>
       </c>
       <c r="S2" t="n">
-        <v>3361639000</v>
+        <v>3270393000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1450799000</v>
+        <v>33697000</v>
       </c>
       <c r="W2" t="n">
-        <v>1450799000</v>
+        <v>33697000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1450799000</v>
+        <v>33697000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-400534000</v>
+        <v>-157336000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1851333000</v>
+        <v>191033000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1851333000</v>
+        <v>191033000</v>
       </c>
       <c r="AC2" t="n">
-        <v>377555000</v>
+        <v>90650000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2228888000</v>
+        <v>281683000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-43435000</v>
+        <v>-65713000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-457416000</v>
+        <v>-417932000</v>
       </c>
       <c r="AG2" t="n">
-        <v>47233000</v>
+        <v>129814000</v>
       </c>
       <c r="AH2" t="n">
-        <v>8339000</v>
+        <v>140385000</v>
       </c>
       <c r="AI2" t="n">
-        <v>401844000</v>
+        <v>147733000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-343856000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>95795000</v>
-      </c>
+        <v>-427230000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>448799000</v>
+        <v>607867000</v>
       </c>
       <c r="AM2" t="n">
-        <v>200738000</v>
+        <v>180637000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3034796000</v>
+        <v>1207947000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1487157000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>1484130000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>34056000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>1522057000</v>
+        <v>1527304000</v>
       </c>
       <c r="AR2" t="n">
-        <v>48470000</v>
+        <v>31460000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1473587000</v>
+        <v>1495844000</v>
       </c>
       <c r="AT2" t="n">
-        <v>4521953000</v>
+        <v>2692077000</v>
       </c>
       <c r="AU2" t="n">
-        <v>7028727000</v>
+        <v>4167369000</v>
       </c>
       <c r="AV2" t="n">
-        <v>11550680000</v>
+        <v>6859446000</v>
       </c>
       <c r="AW2" t="n">
-        <v>11550680000</v>
+        <v>6859446000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-142831207.3</v>
+        <v>-53502948.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2557</v>
+        <v>0.2422</v>
       </c>
       <c r="D3" t="n">
-        <v>3252847000</v>
+        <v>2420810000</v>
       </c>
       <c r="E3" t="n">
-        <v>-558589000</v>
+        <v>-194682000</v>
       </c>
       <c r="F3" t="n">
-        <v>-558589000</v>
+        <v>-220904000</v>
       </c>
       <c r="G3" t="n">
-        <v>686430000</v>
+        <v>401952000</v>
       </c>
       <c r="H3" t="n">
-        <v>992836000</v>
+        <v>982669000</v>
       </c>
       <c r="I3" t="n">
-        <v>5053333000</v>
+        <v>5229645000</v>
       </c>
       <c r="J3" t="n">
-        <v>2694258000</v>
+        <v>2226128000</v>
       </c>
       <c r="K3" t="n">
-        <v>1701422000</v>
+        <v>1243459000</v>
       </c>
       <c r="L3" t="n">
-        <v>-344070000</v>
+        <v>-320459000</v>
       </c>
       <c r="M3" t="n">
-        <v>574897000</v>
+        <v>504254000</v>
       </c>
       <c r="N3" t="n">
-        <v>263624000</v>
+        <v>212732000</v>
       </c>
       <c r="O3" t="n">
-        <v>1102187792.7</v>
+        <v>595575051.2</v>
       </c>
       <c r="P3" t="n">
-        <v>686430000</v>
+        <v>401952000</v>
       </c>
       <c r="Q3" t="n">
-        <v>6337699000</v>
+        <v>6558025000</v>
       </c>
       <c r="R3" t="n">
         <v>3270393000</v>
@@ -871,147 +871,147 @@
         <v>3270393000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>686430000</v>
+        <v>401952000</v>
       </c>
       <c r="W3" t="n">
-        <v>686430000</v>
+        <v>401952000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>686430000</v>
+        <v>401952000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-151988000</v>
+        <v>-158234000</v>
       </c>
       <c r="AA3" t="n">
-        <v>838418000</v>
+        <v>560186000</v>
       </c>
       <c r="AB3" t="n">
-        <v>838418000</v>
+        <v>560186000</v>
       </c>
       <c r="AC3" t="n">
-        <v>288107000</v>
+        <v>179019000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1126525000</v>
+        <v>739205000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-64939000</v>
+        <v>-81868000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-497694000</v>
+        <v>-377650000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-30190000</v>
+        <v>-1740000</v>
       </c>
       <c r="AH3" t="n">
-        <v>156503000</v>
+        <v>102226000</v>
       </c>
       <c r="AI3" t="n">
-        <v>371381000</v>
+        <v>250942000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-344070000</v>
+        <v>-320459000</v>
       </c>
       <c r="AK3" t="n">
-        <v>32797000</v>
+        <v>28937000</v>
       </c>
       <c r="AL3" t="n">
-        <v>574897000</v>
+        <v>504254000</v>
       </c>
       <c r="AM3" t="n">
-        <v>263624000</v>
+        <v>212732000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2085919000</v>
+        <v>1327532000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1284366000</v>
+        <v>1328380000</v>
       </c>
       <c r="AP3" t="n">
-        <v>17015000</v>
+        <v>42430000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1333473000</v>
+        <v>1339433000</v>
       </c>
       <c r="AR3" t="n">
-        <v>31401000</v>
+        <v>33126000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1302072000</v>
+        <v>1306307000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3370285000</v>
+        <v>2655912000</v>
       </c>
       <c r="AU3" t="n">
-        <v>5053333000</v>
+        <v>5229645000</v>
       </c>
       <c r="AV3" t="n">
-        <v>8423618000</v>
+        <v>7885557000</v>
       </c>
       <c r="AW3" t="n">
-        <v>8423618000</v>
+        <v>7885557000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-53502948.8</v>
+        <v>-142831207.3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2422</v>
+        <v>0.2557</v>
       </c>
       <c r="D4" t="n">
-        <v>2420810000</v>
+        <v>3252847000</v>
       </c>
       <c r="E4" t="n">
-        <v>-194682000</v>
+        <v>-558589000</v>
       </c>
       <c r="F4" t="n">
-        <v>-220904000</v>
+        <v>-558589000</v>
       </c>
       <c r="G4" t="n">
-        <v>401952000</v>
+        <v>686430000</v>
       </c>
       <c r="H4" t="n">
-        <v>982669000</v>
+        <v>992836000</v>
       </c>
       <c r="I4" t="n">
-        <v>5229645000</v>
+        <v>5053333000</v>
       </c>
       <c r="J4" t="n">
-        <v>2226128000</v>
+        <v>2694258000</v>
       </c>
       <c r="K4" t="n">
-        <v>1243459000</v>
+        <v>1701422000</v>
       </c>
       <c r="L4" t="n">
-        <v>-320459000</v>
+        <v>-344070000</v>
       </c>
       <c r="M4" t="n">
-        <v>504254000</v>
+        <v>574897000</v>
       </c>
       <c r="N4" t="n">
-        <v>212732000</v>
+        <v>263624000</v>
       </c>
       <c r="O4" t="n">
-        <v>595575051.2</v>
+        <v>1102187792.7</v>
       </c>
       <c r="P4" t="n">
-        <v>401952000</v>
+        <v>686430000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6558025000</v>
+        <v>6337699000</v>
       </c>
       <c r="R4" t="n">
         <v>3270393000</v>
@@ -1020,241 +1020,241 @@
         <v>3270393000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="V4" t="n">
-        <v>401952000</v>
+        <v>686430000</v>
       </c>
       <c r="W4" t="n">
-        <v>401952000</v>
+        <v>686430000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>401952000</v>
+        <v>686430000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-158234000</v>
+        <v>-151988000</v>
       </c>
       <c r="AA4" t="n">
-        <v>560186000</v>
+        <v>838418000</v>
       </c>
       <c r="AB4" t="n">
-        <v>560186000</v>
+        <v>838418000</v>
       </c>
       <c r="AC4" t="n">
-        <v>179019000</v>
+        <v>288107000</v>
       </c>
       <c r="AD4" t="n">
-        <v>739205000</v>
+        <v>1126525000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-81868000</v>
+        <v>-64939000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-377650000</v>
+        <v>-497694000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1740000</v>
+        <v>-30190000</v>
       </c>
       <c r="AH4" t="n">
-        <v>102226000</v>
+        <v>156503000</v>
       </c>
       <c r="AI4" t="n">
-        <v>250942000</v>
+        <v>371381000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-320459000</v>
+        <v>-344070000</v>
       </c>
       <c r="AK4" t="n">
-        <v>28937000</v>
+        <v>32797000</v>
       </c>
       <c r="AL4" t="n">
-        <v>504254000</v>
+        <v>574897000</v>
       </c>
       <c r="AM4" t="n">
-        <v>212732000</v>
+        <v>263624000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1327532000</v>
+        <v>2085919000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1328380000</v>
+        <v>1284366000</v>
       </c>
       <c r="AP4" t="n">
-        <v>42430000</v>
+        <v>17015000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1339433000</v>
+        <v>1333473000</v>
       </c>
       <c r="AR4" t="n">
-        <v>33126000</v>
+        <v>31401000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1306307000</v>
+        <v>1302072000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2655912000</v>
+        <v>3370285000</v>
       </c>
       <c r="AU4" t="n">
-        <v>5229645000</v>
+        <v>5053333000</v>
       </c>
       <c r="AV4" t="n">
-        <v>7885557000</v>
+        <v>8423618000</v>
       </c>
       <c r="AW4" t="n">
-        <v>7885557000</v>
+        <v>8423618000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-147835674</v>
+        <v>-76839437.01971599</v>
       </c>
       <c r="C5" t="n">
-        <v>0.322</v>
+        <v>0.169392</v>
       </c>
       <c r="D5" t="n">
-        <v>2223160000</v>
+        <v>4480201000</v>
       </c>
       <c r="E5" t="n">
-        <v>-459117000</v>
+        <v>-453620000</v>
       </c>
       <c r="F5" t="n">
-        <v>-459117000</v>
+        <v>-453620000</v>
       </c>
       <c r="G5" t="n">
-        <v>33697000</v>
+        <v>1450799000</v>
       </c>
       <c r="H5" t="n">
-        <v>874493000</v>
+        <v>1348894000</v>
       </c>
       <c r="I5" t="n">
-        <v>4167369000</v>
+        <v>7028727000</v>
       </c>
       <c r="J5" t="n">
-        <v>1764043000</v>
+        <v>4026581000</v>
       </c>
       <c r="K5" t="n">
-        <v>889550000</v>
+        <v>2677687000</v>
       </c>
       <c r="L5" t="n">
-        <v>-427230000</v>
+        <v>-343856000</v>
       </c>
       <c r="M5" t="n">
-        <v>607867000</v>
+        <v>448799000</v>
       </c>
       <c r="N5" t="n">
-        <v>180637000</v>
+        <v>200738000</v>
       </c>
       <c r="O5" t="n">
-        <v>344978326</v>
+        <v>1827579562.980284</v>
       </c>
       <c r="P5" t="n">
-        <v>33697000</v>
+        <v>1450799000</v>
       </c>
       <c r="Q5" t="n">
-        <v>5651499000</v>
+        <v>8515884000</v>
       </c>
       <c r="R5" t="n">
-        <v>3270393000</v>
+        <v>3361639000</v>
       </c>
       <c r="S5" t="n">
-        <v>3270393000</v>
+        <v>3361639000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="V5" t="n">
-        <v>33697000</v>
+        <v>1450799000</v>
       </c>
       <c r="W5" t="n">
-        <v>33697000</v>
+        <v>1450799000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>33697000</v>
+        <v>1450799000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-157336000</v>
+        <v>-400534000</v>
       </c>
       <c r="AA5" t="n">
-        <v>191033000</v>
+        <v>1851333000</v>
       </c>
       <c r="AB5" t="n">
-        <v>191033000</v>
+        <v>1851333000</v>
       </c>
       <c r="AC5" t="n">
-        <v>90650000</v>
+        <v>377555000</v>
       </c>
       <c r="AD5" t="n">
-        <v>281683000</v>
+        <v>2228888000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-65713000</v>
+        <v>-43435000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-417932000</v>
+        <v>-457416000</v>
       </c>
       <c r="AG5" t="n">
-        <v>129814000</v>
+        <v>47233000</v>
       </c>
       <c r="AH5" t="n">
-        <v>140385000</v>
+        <v>8339000</v>
       </c>
       <c r="AI5" t="n">
-        <v>147733000</v>
+        <v>401844000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-427230000</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>-343856000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>95795000</v>
+      </c>
       <c r="AL5" t="n">
-        <v>607867000</v>
+        <v>448799000</v>
       </c>
       <c r="AM5" t="n">
-        <v>180637000</v>
+        <v>200738000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1207947000</v>
+        <v>3034796000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1484130000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>34056000</v>
-      </c>
+        <v>1487157000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>1527304000</v>
+        <v>1522057000</v>
       </c>
       <c r="AR5" t="n">
-        <v>31460000</v>
+        <v>48470000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1495844000</v>
+        <v>1473587000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2692077000</v>
+        <v>4521953000</v>
       </c>
       <c r="AU5" t="n">
-        <v>4167369000</v>
+        <v>7028727000</v>
       </c>
       <c r="AV5" t="n">
-        <v>6859446000</v>
+        <v>11550680000</v>
       </c>
       <c r="AW5" t="n">
-        <v>6859446000</v>
+        <v>11550680000</v>
       </c>
     </row>
   </sheetData>
@@ -1655,238 +1655,236 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3402393204</v>
+        <v>3270393204</v>
       </c>
       <c r="C2" t="n">
-        <v>3402393204</v>
+        <v>3270393204</v>
       </c>
       <c r="D2" t="n">
-        <v>15153605000</v>
+        <v>11057237000</v>
       </c>
       <c r="E2" t="n">
-        <v>20051363000</v>
+        <v>16905637000</v>
       </c>
       <c r="F2" t="n">
-        <v>20546374000</v>
+        <v>15619532000</v>
       </c>
       <c r="G2" t="n">
-        <v>38367032000</v>
+        <v>30357792000</v>
       </c>
       <c r="H2" t="n">
-        <v>-544207000</v>
+        <v>-4148099000</v>
       </c>
       <c r="I2" t="n">
-        <v>20546374000</v>
+        <v>15619532000</v>
       </c>
       <c r="J2" t="n">
-        <v>2867933000</v>
+        <v>2850187000</v>
       </c>
       <c r="K2" t="n">
-        <v>21183602000</v>
+        <v>16302342000</v>
       </c>
       <c r="L2" t="n">
-        <v>31591466000</v>
+        <v>21902092000</v>
       </c>
       <c r="M2" t="n">
-        <v>25192291000</v>
+        <v>19728874000</v>
       </c>
       <c r="N2" t="n">
-        <v>4008689000</v>
+        <v>3426532000</v>
       </c>
       <c r="O2" t="n">
-        <v>21183602000</v>
+        <v>16302342000</v>
       </c>
       <c r="P2" t="n">
-        <v>7025278000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5741204000</v>
-      </c>
+        <v>4539287000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>3402393000</v>
+        <v>3270393000</v>
       </c>
       <c r="S2" t="n">
-        <v>3402393000</v>
+        <v>3270393000</v>
       </c>
       <c r="T2" t="n">
-        <v>28375654000</v>
+        <v>23293732000</v>
       </c>
       <c r="U2" t="n">
-        <v>13940497000</v>
+        <v>7520639000</v>
       </c>
       <c r="V2" t="n">
-        <v>1610437000</v>
+        <v>1408881000</v>
       </c>
       <c r="W2" t="n">
-        <v>576498000</v>
+        <v>137805000</v>
       </c>
       <c r="X2" t="n">
-        <v>1162730000</v>
+        <v>310685000</v>
       </c>
       <c r="Y2" t="n">
-        <v>10466343000</v>
+        <v>5620920000</v>
       </c>
       <c r="Z2" t="n">
-        <v>58479000</v>
+        <v>21170000</v>
       </c>
       <c r="AA2" t="n">
-        <v>10407864000</v>
+        <v>5599750000</v>
       </c>
       <c r="AB2" t="n">
-        <v>124489000</v>
+        <v>42348000</v>
       </c>
       <c r="AC2" t="n">
-        <v>14435157000</v>
+        <v>15773093000</v>
       </c>
       <c r="AD2" t="n">
-        <v>248254000</v>
+        <v>249741000</v>
       </c>
       <c r="AE2" t="n">
-        <v>9585020000</v>
+        <v>11284717000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2809454000</v>
+        <v>2829017000</v>
       </c>
       <c r="AG2" t="n">
-        <v>6775566000</v>
+        <v>8455700000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1607000</v>
+        <v>4836000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1909680000</v>
+        <v>1048319000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>755810000</v>
+        <v>510035000</v>
       </c>
       <c r="AK2" t="n">
-        <v>328152000</v>
+        <v>149041000</v>
       </c>
       <c r="AL2" t="n">
-        <v>825718000</v>
+        <v>389243000</v>
       </c>
       <c r="AM2" t="n">
-        <v>53567945000</v>
+        <v>43022606000</v>
       </c>
       <c r="AN2" t="n">
-        <v>39676995000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>31397612000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>766478000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>64502000</v>
+        <v>56575000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>509564000</v>
+        <v>281511000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1428628000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>253418000</v>
-      </c>
+        <v>1085659000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>1175210000</v>
+        <v>1085659000</v>
       </c>
       <c r="AU2" t="n">
-        <v>412169000</v>
+        <v>693754000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1716000</v>
+        <v>4082000</v>
       </c>
       <c r="AW2" t="n">
-        <v>410453000</v>
+        <v>689672000</v>
       </c>
       <c r="AX2" t="n">
-        <v>76443000</v>
+        <v>84894000</v>
       </c>
       <c r="AY2" t="n">
-        <v>637228000</v>
+        <v>682810000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>53925000</v>
+        <v>73285000</v>
       </c>
       <c r="BA2" t="n">
-        <v>583303000</v>
+        <v>609525000</v>
       </c>
       <c r="BB2" t="n">
-        <v>36328945000</v>
+        <v>28219909000</v>
       </c>
       <c r="BC2" t="n">
-        <v>-14275073000</v>
+        <v>-10607190000</v>
       </c>
       <c r="BD2" t="n">
-        <v>50604018000</v>
+        <v>38827099000</v>
       </c>
       <c r="BE2" t="n">
-        <v>4852704000</v>
+        <v>3512881000</v>
       </c>
       <c r="BF2" t="n">
-        <v>51891000</v>
+        <v>2366000</v>
       </c>
       <c r="BG2" t="n">
-        <v>5174935000</v>
+        <v>4444303000</v>
       </c>
       <c r="BH2" t="n">
-        <v>7353085000</v>
+        <v>6411059000</v>
       </c>
       <c r="BI2" t="n">
-        <v>740333000</v>
+        <v>738808000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>32431070000</v>
+        <v>23717682000</v>
       </c>
       <c r="BK2" t="n">
-        <v>13890950000</v>
+        <v>11624994000</v>
       </c>
       <c r="BL2" t="n">
-        <v>625805000</v>
+        <v>407268000</v>
       </c>
       <c r="BM2" t="n">
-        <v>375595000</v>
+        <v>143889000</v>
       </c>
       <c r="BN2" t="n">
-        <v>6246351000</v>
+        <v>4180883000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-9983000</v>
+        <v>-35672000</v>
       </c>
       <c r="BP2" t="n">
-        <v>106380000</v>
+        <v>111916000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5939518000</v>
+        <v>3956924000</v>
       </c>
       <c r="BR2" t="n">
-        <v>210436000</v>
+        <v>147715000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2878146000</v>
+        <v>2477572000</v>
       </c>
       <c r="BT2" t="n">
-        <v>177284000</v>
+        <v>172257000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3587769000</v>
+        <v>4243125000</v>
       </c>
       <c r="BV2" t="n">
-        <v>1557944000</v>
+        <v>1244912000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2029825000</v>
+        <v>2998213000</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>45000000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2029825000</v>
+        <v>2953213000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>3270393204</v>
@@ -1895,46 +1893,46 @@
         <v>3270393204</v>
       </c>
       <c r="D3" t="n">
-        <v>12930098000</v>
+        <v>12589278000</v>
       </c>
       <c r="E3" t="n">
-        <v>17786878000</v>
+        <v>18809594000</v>
       </c>
       <c r="F3" t="n">
-        <v>18211062000</v>
+        <v>15958377000</v>
       </c>
       <c r="G3" t="n">
-        <v>34708161000</v>
+        <v>32782434000</v>
       </c>
       <c r="H3" t="n">
-        <v>793171000</v>
+        <v>-2620454000</v>
       </c>
       <c r="I3" t="n">
-        <v>18211062000</v>
+        <v>15958377000</v>
       </c>
       <c r="J3" t="n">
-        <v>1940677000</v>
+        <v>2637103000</v>
       </c>
       <c r="K3" t="n">
-        <v>18861960000</v>
+        <v>16609943000</v>
       </c>
       <c r="L3" t="n">
-        <v>28801298000</v>
+        <v>24763389000</v>
       </c>
       <c r="M3" t="n">
-        <v>22244326000</v>
+        <v>20047452000</v>
       </c>
       <c r="N3" t="n">
-        <v>3382366000</v>
+        <v>3437509000</v>
       </c>
       <c r="O3" t="n">
-        <v>18861960000</v>
+        <v>16609943000</v>
       </c>
       <c r="P3" t="n">
-        <v>7075529000</v>
+        <v>5058253000</v>
       </c>
       <c r="Q3" t="n">
-        <v>4815635000</v>
+        <v>4590929000</v>
       </c>
       <c r="R3" t="n">
         <v>3270393000</v>
@@ -1943,181 +1941,181 @@
         <v>3270393000</v>
       </c>
       <c r="T3" t="n">
-        <v>24623070000</v>
+        <v>25840043000</v>
       </c>
       <c r="U3" t="n">
-        <v>12379379000</v>
+        <v>10268789000</v>
       </c>
       <c r="V3" t="n">
-        <v>1597632000</v>
+        <v>1655290000</v>
       </c>
       <c r="W3" t="n">
-        <v>480953000</v>
+        <v>127975000</v>
       </c>
       <c r="X3" t="n">
-        <v>264159000</v>
+        <v>274346000</v>
       </c>
       <c r="Y3" t="n">
-        <v>9958567000</v>
+        <v>8168502000</v>
       </c>
       <c r="Z3" t="n">
-        <v>19229000</v>
+        <v>15056000</v>
       </c>
       <c r="AA3" t="n">
-        <v>9939338000</v>
+        <v>8153446000</v>
       </c>
       <c r="AB3" t="n">
-        <v>78068000</v>
+        <v>42676000</v>
       </c>
       <c r="AC3" t="n">
-        <v>12243691000</v>
+        <v>15571254000</v>
       </c>
       <c r="AD3" t="n">
-        <v>221854000</v>
+        <v>197668000</v>
       </c>
       <c r="AE3" t="n">
-        <v>7828311000</v>
+        <v>10641092000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1921448000</v>
+        <v>2622047000</v>
       </c>
       <c r="AG3" t="n">
-        <v>5906863000</v>
+        <v>8019045000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2378000</v>
+        <v>1970000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1300944000</v>
+        <v>1207010000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>671213000</v>
+        <v>668603000</v>
       </c>
       <c r="AK3" t="n">
-        <v>108977000</v>
+        <v>107770000</v>
       </c>
       <c r="AL3" t="n">
-        <v>520754000</v>
+        <v>430637000</v>
       </c>
       <c r="AM3" t="n">
-        <v>46867396000</v>
+        <v>45887495000</v>
       </c>
       <c r="AN3" t="n">
-        <v>33830534000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>32936695000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>856079000</v>
+      </c>
       <c r="AP3" t="n">
-        <v>71752000</v>
+        <v>53933000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>439869000</v>
+        <v>362346000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1791520000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>562662000</v>
-      </c>
+        <v>1009743000</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1228858000</v>
+        <v>1009743000</v>
       </c>
       <c r="AU3" t="n">
-        <v>267713000</v>
+        <v>900955000</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>4089000</v>
       </c>
       <c r="AW3" t="n">
-        <v>267713000</v>
+        <v>896866000</v>
       </c>
       <c r="AX3" t="n">
-        <v>93011000</v>
+        <v>82057000</v>
       </c>
       <c r="AY3" t="n">
-        <v>650898000</v>
+        <v>651566000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>67595000</v>
+        <v>68263000</v>
       </c>
       <c r="BA3" t="n">
         <v>583303000</v>
       </c>
       <c r="BB3" t="n">
-        <v>30282731000</v>
+        <v>29524182000</v>
       </c>
       <c r="BC3" t="n">
-        <v>-12816848000</v>
+        <v>-11624594000</v>
       </c>
       <c r="BD3" t="n">
-        <v>43099579000</v>
+        <v>41148776000</v>
       </c>
       <c r="BE3" t="n">
-        <v>4486011000</v>
+        <v>4096101000</v>
       </c>
       <c r="BF3" t="n">
-        <v>7160000</v>
+        <v>9201000</v>
       </c>
       <c r="BG3" t="n">
-        <v>4882489000</v>
+        <v>4652213000</v>
       </c>
       <c r="BH3" t="n">
-        <v>6731321000</v>
+        <v>6601385000</v>
       </c>
       <c r="BI3" t="n">
-        <v>745198000</v>
+        <v>696184000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>26247400000</v>
+        <v>25093692000</v>
       </c>
       <c r="BK3" t="n">
-        <v>13036862000</v>
+        <v>12950800000</v>
       </c>
       <c r="BL3" t="n">
-        <v>536768000</v>
+        <v>367405000</v>
       </c>
       <c r="BM3" t="n">
-        <v>170723000</v>
+        <v>185780000</v>
       </c>
       <c r="BN3" t="n">
-        <v>5154577000</v>
+        <v>4670644000</v>
       </c>
       <c r="BO3" t="n">
-        <v>-21228000</v>
+        <v>-41878000</v>
       </c>
       <c r="BP3" t="n">
-        <v>76165000</v>
+        <v>77723000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4989301000</v>
+        <v>4486808000</v>
       </c>
       <c r="BR3" t="n">
-        <v>110339000</v>
+        <v>147991000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2498938000</v>
+        <v>2405198000</v>
       </c>
       <c r="BT3" t="n">
-        <v>238950000</v>
+        <v>207539000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4436906000</v>
+        <v>5114234000</v>
       </c>
       <c r="BV3" t="n">
-        <v>1520803000</v>
+        <v>1531021000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2916103000</v>
+        <v>3583213000</v>
       </c>
       <c r="BX3" t="n">
-        <v>116202000</v>
+        <v>235000000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2799901000</v>
+        <v>3348213000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>3270393204</v>
@@ -2126,46 +2124,46 @@
         <v>3270393204</v>
       </c>
       <c r="D4" t="n">
-        <v>12589278000</v>
+        <v>12930098000</v>
       </c>
       <c r="E4" t="n">
-        <v>18809594000</v>
+        <v>17786878000</v>
       </c>
       <c r="F4" t="n">
-        <v>15958377000</v>
+        <v>18211062000</v>
       </c>
       <c r="G4" t="n">
-        <v>32782434000</v>
+        <v>34708161000</v>
       </c>
       <c r="H4" t="n">
-        <v>-2620454000</v>
+        <v>793171000</v>
       </c>
       <c r="I4" t="n">
-        <v>15958377000</v>
+        <v>18211062000</v>
       </c>
       <c r="J4" t="n">
-        <v>2637103000</v>
+        <v>1940677000</v>
       </c>
       <c r="K4" t="n">
-        <v>16609943000</v>
+        <v>18861960000</v>
       </c>
       <c r="L4" t="n">
-        <v>24763389000</v>
+        <v>28801298000</v>
       </c>
       <c r="M4" t="n">
-        <v>20047452000</v>
+        <v>22244326000</v>
       </c>
       <c r="N4" t="n">
-        <v>3437509000</v>
+        <v>3382366000</v>
       </c>
       <c r="O4" t="n">
-        <v>16609943000</v>
+        <v>18861960000</v>
       </c>
       <c r="P4" t="n">
-        <v>5058253000</v>
+        <v>7075529000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4590929000</v>
+        <v>4815635000</v>
       </c>
       <c r="R4" t="n">
         <v>3270393000</v>
@@ -2174,405 +2172,407 @@
         <v>3270393000</v>
       </c>
       <c r="T4" t="n">
-        <v>25840043000</v>
+        <v>24623070000</v>
       </c>
       <c r="U4" t="n">
-        <v>10268789000</v>
+        <v>12379379000</v>
       </c>
       <c r="V4" t="n">
-        <v>1655290000</v>
+        <v>1597632000</v>
       </c>
       <c r="W4" t="n">
-        <v>127975000</v>
+        <v>480953000</v>
       </c>
       <c r="X4" t="n">
-        <v>274346000</v>
+        <v>264159000</v>
       </c>
       <c r="Y4" t="n">
-        <v>8168502000</v>
+        <v>9958567000</v>
       </c>
       <c r="Z4" t="n">
-        <v>15056000</v>
+        <v>19229000</v>
       </c>
       <c r="AA4" t="n">
-        <v>8153446000</v>
+        <v>9939338000</v>
       </c>
       <c r="AB4" t="n">
-        <v>42676000</v>
+        <v>78068000</v>
       </c>
       <c r="AC4" t="n">
-        <v>15571254000</v>
+        <v>12243691000</v>
       </c>
       <c r="AD4" t="n">
-        <v>197668000</v>
+        <v>221854000</v>
       </c>
       <c r="AE4" t="n">
-        <v>10641092000</v>
+        <v>7828311000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2622047000</v>
+        <v>1921448000</v>
       </c>
       <c r="AG4" t="n">
-        <v>8019045000</v>
+        <v>5906863000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1970000</v>
+        <v>2378000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1207010000</v>
+        <v>1300944000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>668603000</v>
+        <v>671213000</v>
       </c>
       <c r="AK4" t="n">
-        <v>107770000</v>
+        <v>108977000</v>
       </c>
       <c r="AL4" t="n">
-        <v>430637000</v>
+        <v>520754000</v>
       </c>
       <c r="AM4" t="n">
-        <v>45887495000</v>
+        <v>46867396000</v>
       </c>
       <c r="AN4" t="n">
-        <v>32936695000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>856079000</v>
-      </c>
+        <v>33830534000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>53933000</v>
+        <v>71752000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>362346000</v>
+        <v>439869000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1009743000</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>1791520000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>562662000</v>
+      </c>
       <c r="AT4" t="n">
-        <v>1009743000</v>
+        <v>1228858000</v>
       </c>
       <c r="AU4" t="n">
-        <v>900955000</v>
+        <v>267713000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4089000</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>896866000</v>
+        <v>267713000</v>
       </c>
       <c r="AX4" t="n">
-        <v>82057000</v>
+        <v>93011000</v>
       </c>
       <c r="AY4" t="n">
-        <v>651566000</v>
+        <v>650898000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>68263000</v>
+        <v>67595000</v>
       </c>
       <c r="BA4" t="n">
         <v>583303000</v>
       </c>
       <c r="BB4" t="n">
-        <v>29524182000</v>
+        <v>30282731000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-11624594000</v>
+        <v>-12816848000</v>
       </c>
       <c r="BD4" t="n">
-        <v>41148776000</v>
+        <v>43099579000</v>
       </c>
       <c r="BE4" t="n">
-        <v>4096101000</v>
+        <v>4486011000</v>
       </c>
       <c r="BF4" t="n">
-        <v>9201000</v>
+        <v>7160000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4652213000</v>
+        <v>4882489000</v>
       </c>
       <c r="BH4" t="n">
-        <v>6601385000</v>
+        <v>6731321000</v>
       </c>
       <c r="BI4" t="n">
-        <v>696184000</v>
+        <v>745198000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>25093692000</v>
+        <v>26247400000</v>
       </c>
       <c r="BK4" t="n">
-        <v>12950800000</v>
+        <v>13036862000</v>
       </c>
       <c r="BL4" t="n">
-        <v>367405000</v>
+        <v>536768000</v>
       </c>
       <c r="BM4" t="n">
-        <v>185780000</v>
+        <v>170723000</v>
       </c>
       <c r="BN4" t="n">
-        <v>4670644000</v>
+        <v>5154577000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-41878000</v>
+        <v>-21228000</v>
       </c>
       <c r="BP4" t="n">
-        <v>77723000</v>
+        <v>76165000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4486808000</v>
+        <v>4989301000</v>
       </c>
       <c r="BR4" t="n">
-        <v>147991000</v>
+        <v>110339000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2405198000</v>
+        <v>2498938000</v>
       </c>
       <c r="BT4" t="n">
-        <v>207539000</v>
+        <v>238950000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5114234000</v>
+        <v>4436906000</v>
       </c>
       <c r="BV4" t="n">
-        <v>1531021000</v>
+        <v>1520803000</v>
       </c>
       <c r="BW4" t="n">
-        <v>3583213000</v>
+        <v>2916103000</v>
       </c>
       <c r="BX4" t="n">
-        <v>235000000</v>
+        <v>116202000</v>
       </c>
       <c r="BY4" t="n">
-        <v>3348213000</v>
+        <v>2799901000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>3270393204</v>
+        <v>3402393204</v>
       </c>
       <c r="C5" t="n">
-        <v>3270393204</v>
+        <v>3402393204</v>
       </c>
       <c r="D5" t="n">
-        <v>11057237000</v>
+        <v>15153605000</v>
       </c>
       <c r="E5" t="n">
-        <v>16905637000</v>
+        <v>20051363000</v>
       </c>
       <c r="F5" t="n">
-        <v>15619532000</v>
+        <v>20546374000</v>
       </c>
       <c r="G5" t="n">
-        <v>30357792000</v>
+        <v>38367032000</v>
       </c>
       <c r="H5" t="n">
-        <v>-4148099000</v>
+        <v>-544207000</v>
       </c>
       <c r="I5" t="n">
-        <v>15619532000</v>
+        <v>20546374000</v>
       </c>
       <c r="J5" t="n">
-        <v>2850187000</v>
+        <v>2867933000</v>
       </c>
       <c r="K5" t="n">
-        <v>16302342000</v>
+        <v>21183602000</v>
       </c>
       <c r="L5" t="n">
-        <v>21902092000</v>
+        <v>31591466000</v>
       </c>
       <c r="M5" t="n">
-        <v>19728874000</v>
+        <v>25192291000</v>
       </c>
       <c r="N5" t="n">
-        <v>3426532000</v>
+        <v>4008689000</v>
       </c>
       <c r="O5" t="n">
-        <v>16302342000</v>
+        <v>21183602000</v>
       </c>
       <c r="P5" t="n">
-        <v>4539287000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>7025278000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5741204000</v>
+      </c>
       <c r="R5" t="n">
-        <v>3270393000</v>
+        <v>3402393000</v>
       </c>
       <c r="S5" t="n">
-        <v>3270393000</v>
+        <v>3402393000</v>
       </c>
       <c r="T5" t="n">
-        <v>23293732000</v>
+        <v>28375654000</v>
       </c>
       <c r="U5" t="n">
-        <v>7520639000</v>
+        <v>13940497000</v>
       </c>
       <c r="V5" t="n">
-        <v>1408881000</v>
+        <v>1610437000</v>
       </c>
       <c r="W5" t="n">
-        <v>137805000</v>
+        <v>576498000</v>
       </c>
       <c r="X5" t="n">
-        <v>310685000</v>
+        <v>1162730000</v>
       </c>
       <c r="Y5" t="n">
-        <v>5620920000</v>
+        <v>10466343000</v>
       </c>
       <c r="Z5" t="n">
-        <v>21170000</v>
+        <v>58479000</v>
       </c>
       <c r="AA5" t="n">
-        <v>5599750000</v>
+        <v>10407864000</v>
       </c>
       <c r="AB5" t="n">
-        <v>42348000</v>
+        <v>124489000</v>
       </c>
       <c r="AC5" t="n">
-        <v>15773093000</v>
+        <v>14435157000</v>
       </c>
       <c r="AD5" t="n">
-        <v>249741000</v>
+        <v>248254000</v>
       </c>
       <c r="AE5" t="n">
-        <v>11284717000</v>
+        <v>9585020000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2829017000</v>
+        <v>2809454000</v>
       </c>
       <c r="AG5" t="n">
-        <v>8455700000</v>
+        <v>6775566000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4836000</v>
+        <v>1607000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1048319000</v>
+        <v>1909680000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>510035000</v>
+        <v>755810000</v>
       </c>
       <c r="AK5" t="n">
-        <v>149041000</v>
+        <v>328152000</v>
       </c>
       <c r="AL5" t="n">
-        <v>389243000</v>
+        <v>825718000</v>
       </c>
       <c r="AM5" t="n">
-        <v>43022606000</v>
+        <v>53567945000</v>
       </c>
       <c r="AN5" t="n">
-        <v>31397612000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>766478000</v>
-      </c>
+        <v>39676995000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>56575000</v>
+        <v>64502000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>281511000</v>
+        <v>509564000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1085659000</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>1428628000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>253418000</v>
+      </c>
       <c r="AT5" t="n">
-        <v>1085659000</v>
+        <v>1175210000</v>
       </c>
       <c r="AU5" t="n">
-        <v>693754000</v>
+        <v>412169000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4082000</v>
+        <v>1716000</v>
       </c>
       <c r="AW5" t="n">
-        <v>689672000</v>
+        <v>410453000</v>
       </c>
       <c r="AX5" t="n">
-        <v>84894000</v>
+        <v>76443000</v>
       </c>
       <c r="AY5" t="n">
-        <v>682810000</v>
+        <v>637228000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>73285000</v>
+        <v>53925000</v>
       </c>
       <c r="BA5" t="n">
-        <v>609525000</v>
+        <v>583303000</v>
       </c>
       <c r="BB5" t="n">
-        <v>28219909000</v>
+        <v>36328945000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-10607190000</v>
+        <v>-14275073000</v>
       </c>
       <c r="BD5" t="n">
-        <v>38827099000</v>
+        <v>50604018000</v>
       </c>
       <c r="BE5" t="n">
-        <v>3512881000</v>
+        <v>4852704000</v>
       </c>
       <c r="BF5" t="n">
-        <v>2366000</v>
+        <v>51891000</v>
       </c>
       <c r="BG5" t="n">
-        <v>4444303000</v>
+        <v>5174935000</v>
       </c>
       <c r="BH5" t="n">
-        <v>6411059000</v>
+        <v>7353085000</v>
       </c>
       <c r="BI5" t="n">
-        <v>738808000</v>
+        <v>740333000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>23717682000</v>
+        <v>32431070000</v>
       </c>
       <c r="BK5" t="n">
-        <v>11624994000</v>
+        <v>13890950000</v>
       </c>
       <c r="BL5" t="n">
-        <v>407268000</v>
+        <v>625805000</v>
       </c>
       <c r="BM5" t="n">
-        <v>143889000</v>
+        <v>375595000</v>
       </c>
       <c r="BN5" t="n">
-        <v>4180883000</v>
+        <v>6246351000</v>
       </c>
       <c r="BO5" t="n">
-        <v>-35672000</v>
+        <v>-9983000</v>
       </c>
       <c r="BP5" t="n">
-        <v>111916000</v>
+        <v>106380000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3956924000</v>
+        <v>5939518000</v>
       </c>
       <c r="BR5" t="n">
-        <v>147715000</v>
+        <v>210436000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2477572000</v>
+        <v>2878146000</v>
       </c>
       <c r="BT5" t="n">
-        <v>172257000</v>
+        <v>177284000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4243125000</v>
+        <v>3587769000</v>
       </c>
       <c r="BV5" t="n">
-        <v>1244912000</v>
+        <v>1557944000</v>
       </c>
       <c r="BW5" t="n">
-        <v>2998213000</v>
+        <v>2029825000</v>
       </c>
       <c r="BX5" t="n">
-        <v>45000000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>2953213000</v>
+        <v>2029825000</v>
       </c>
     </row>
   </sheetData>
@@ -2858,644 +2858,644 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>527393000</v>
+        <v>419969000</v>
       </c>
       <c r="C2" t="n">
-        <v>-95902000000</v>
+        <v>-62999851000</v>
       </c>
       <c r="D2" t="n">
-        <v>98117403000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1568145000</v>
-      </c>
+        <v>62499371000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-2069772000</v>
+        <v>-2384605000</v>
       </c>
       <c r="G2" t="n">
-        <v>2029825000</v>
+        <v>2998213000</v>
       </c>
       <c r="H2" t="n">
-        <v>2916103000</v>
+        <v>1840469000</v>
       </c>
       <c r="I2" t="n">
-        <v>-2439000</v>
+        <v>-13769000</v>
       </c>
       <c r="J2" t="n">
-        <v>-883839000</v>
+        <v>1171513000</v>
       </c>
       <c r="K2" t="n">
-        <v>1815025000</v>
+        <v>1244442000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1045260000</v>
+        <v>2868608000</v>
       </c>
       <c r="M2" t="n">
-        <v>-595832000</v>
+        <v>-699344000</v>
       </c>
       <c r="N2" t="n">
-        <v>-311167000</v>
+        <v>-410676000</v>
       </c>
       <c r="O2" t="n">
-        <v>-311167000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1568145000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1568145000</v>
-      </c>
+        <v>-410676000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>2215403000</v>
+        <v>-500480000</v>
       </c>
       <c r="S2" t="n">
-        <v>2215403000</v>
+        <v>-500480000</v>
       </c>
       <c r="T2" t="n">
-        <v>-95902000000</v>
+        <v>-62999851000</v>
       </c>
       <c r="U2" t="n">
-        <v>98117403000</v>
+        <v>62499371000</v>
       </c>
       <c r="V2" t="n">
-        <v>-5296029000</v>
+        <v>-2877503000</v>
       </c>
       <c r="W2" t="n">
-        <v>-7066000</v>
+        <v>-118638000</v>
       </c>
       <c r="X2" t="n">
-        <v>62526000</v>
+        <v>14128000</v>
       </c>
       <c r="Y2" t="n">
-        <v>43489000</v>
+        <v>16299000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-92147000</v>
+        <v>-281136000</v>
       </c>
       <c r="AA2" t="n">
-        <v>437095000</v>
+        <v>137883000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-529242000</v>
+        <v>-419019000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3179555000</v>
+        <v>-28448000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1800000</v>
+        <v>250000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3181355000</v>
+        <v>-28698000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-167131000</v>
+        <v>-229765000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-167131000</v>
+        <v>-229765000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1901738000</v>
+        <v>-2148643000</v>
       </c>
       <c r="AI2" t="n">
-        <v>903000</v>
+        <v>6197000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1902641000</v>
+        <v>-2154840000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2597165000</v>
+        <v>2804574000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-523400000</v>
+        <v>-198880000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1324891000</v>
+        <v>915033000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-634514000</v>
+        <v>66698000</v>
       </c>
       <c r="AO2" t="n">
-        <v>247342000</v>
+        <v>138641000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-572908000</v>
+        <v>-100799000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-656759000</v>
+        <v>910752000</v>
       </c>
       <c r="AR2" t="n">
-        <v>293768000</v>
+        <v>-92206000</v>
       </c>
       <c r="AS2" t="n">
-        <v>451490000</v>
+        <v>583553000</v>
       </c>
       <c r="AT2" t="n">
-        <v>18056000</v>
+        <v>39476000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1348894000</v>
+        <v>874493000</v>
       </c>
       <c r="AV2" t="n">
-        <v>341983000</v>
+        <v>78874000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1006911000</v>
+        <v>795619000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-31257000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>41185000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-44653000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>47387000</v>
+        <v>29814000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-154000</v>
+        <v>270000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2228888000</v>
+        <v>281683000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>39025000</v>
+        <v>-1143040000</v>
       </c>
       <c r="C3" t="n">
-        <v>-70354543000</v>
+        <v>-28253891000</v>
       </c>
       <c r="D3" t="n">
-        <v>69339271000</v>
-      </c>
-      <c r="E3" t="n">
+        <v>30182135000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>-1836007000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3583213000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2998213000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>21734000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>563266000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1825348000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>726838000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-716525000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-101187000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-101187000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1928244000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1928244000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-28253891000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>30182135000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-1955049000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-61754000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>93001000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>19212000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>35906000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>308129000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-272223000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-146038000</v>
+      </c>
+      <c r="AD3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>-1793480000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2916103000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3583213000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>12011000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-679121000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-551681000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1504718000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-696151000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-333141000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-333141000</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="AE3" t="n">
+        <v>-146038000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-364060000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-364060000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1457598000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>14349000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-1471947000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>692967000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-328744000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-1444032000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-651118000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-70966000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>147135000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-531036000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-332584000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>457000000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>12175000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>982669000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>107248000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>875421000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-163950000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>30770000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-4297000</v>
+      </c>
+      <c r="BA3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-1015272000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-1015272000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-70354543000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>69339271000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-1959945000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>63280000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>149514000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>35117000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-400177000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>27119000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-427296000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11879000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11879000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-226340000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-226340000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-1565835000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1305000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-1567140000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1832505000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-360279000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-943996000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-10531000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-359909000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-10172000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-488754000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-72082000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>458564000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>37316000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>992836000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>126391000</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>866445000</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>45021000</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2561000</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-32751000</v>
-      </c>
       <c r="BB3" t="n">
-        <v>1126525000</v>
+        <v>739205000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1143040000</v>
+        <v>39025000</v>
       </c>
       <c r="C4" t="n">
-        <v>-28253891000</v>
+        <v>-70354543000</v>
       </c>
       <c r="D4" t="n">
-        <v>30182135000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>69339271000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-1836007000</v>
+        <v>-1793480000</v>
       </c>
       <c r="G4" t="n">
+        <v>2916103000</v>
+      </c>
+      <c r="H4" t="n">
         <v>3583213000</v>
       </c>
-      <c r="H4" t="n">
-        <v>2998213000</v>
-      </c>
       <c r="I4" t="n">
-        <v>21734000</v>
+        <v>12011000</v>
       </c>
       <c r="J4" t="n">
-        <v>563266000</v>
+        <v>-679121000</v>
       </c>
       <c r="K4" t="n">
-        <v>1825348000</v>
+        <v>-551681000</v>
       </c>
       <c r="L4" t="n">
-        <v>726838000</v>
+        <v>1504718000</v>
       </c>
       <c r="M4" t="n">
-        <v>-716525000</v>
+        <v>-696151000</v>
       </c>
       <c r="N4" t="n">
-        <v>-101187000</v>
+        <v>-333141000</v>
       </c>
       <c r="O4" t="n">
-        <v>-101187000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>-333141000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
-        <v>1928244000</v>
+        <v>-1015272000</v>
       </c>
       <c r="S4" t="n">
-        <v>1928244000</v>
+        <v>-1015272000</v>
       </c>
       <c r="T4" t="n">
-        <v>-28253891000</v>
+        <v>-70354543000</v>
       </c>
       <c r="U4" t="n">
-        <v>30182135000</v>
+        <v>69339271000</v>
       </c>
       <c r="V4" t="n">
-        <v>-1955049000</v>
+        <v>-1959945000</v>
       </c>
       <c r="W4" t="n">
-        <v>-61754000</v>
+        <v>63280000</v>
       </c>
       <c r="X4" t="n">
-        <v>93001000</v>
+        <v>149514000</v>
       </c>
       <c r="Y4" t="n">
-        <v>19212000</v>
+        <v>35117000</v>
       </c>
       <c r="Z4" t="n">
-        <v>35906000</v>
+        <v>-400177000</v>
       </c>
       <c r="AA4" t="n">
-        <v>308129000</v>
+        <v>27119000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-272223000</v>
+        <v>-427296000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-146038000</v>
+        <v>11879000</v>
       </c>
       <c r="AD4" t="n">
+        <v>11879000</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="n">
-        <v>-146038000</v>
-      </c>
       <c r="AF4" t="n">
-        <v>-364060000</v>
+        <v>-226340000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-364060000</v>
+        <v>-226340000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1457598000</v>
+        <v>-1565835000</v>
       </c>
       <c r="AI4" t="n">
-        <v>14349000</v>
+        <v>1305000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1471947000</v>
+        <v>-1567140000</v>
       </c>
       <c r="AK4" t="n">
-        <v>692967000</v>
+        <v>1832505000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-328744000</v>
+        <v>-360279000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1444032000</v>
+        <v>-943996000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-651118000</v>
+        <v>-10531000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-70966000</v>
+        <v>-359909000</v>
       </c>
       <c r="AP4" t="n">
-        <v>147135000</v>
+        <v>-10172000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-531036000</v>
+        <v>-488754000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-332584000</v>
+        <v>-72082000</v>
       </c>
       <c r="AS4" t="n">
-        <v>457000000</v>
+        <v>458564000</v>
       </c>
       <c r="AT4" t="n">
-        <v>12175000</v>
+        <v>37316000</v>
       </c>
       <c r="AU4" t="n">
-        <v>982669000</v>
+        <v>992836000</v>
       </c>
       <c r="AV4" t="n">
-        <v>107248000</v>
+        <v>126391000</v>
       </c>
       <c r="AW4" t="n">
-        <v>875421000</v>
+        <v>866445000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-163950000</v>
+        <v>45021000</v>
       </c>
       <c r="AY4" t="n">
-        <v>30770000</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-4297000</v>
+        <v>2561000</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-32751000</v>
       </c>
       <c r="BB4" t="n">
-        <v>739205000</v>
+        <v>1126525000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>419969000</v>
+        <v>527393000</v>
       </c>
       <c r="C5" t="n">
-        <v>-62999851000</v>
+        <v>-95902000000</v>
       </c>
       <c r="D5" t="n">
-        <v>62499371000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>98117403000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1568145000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-2384605000</v>
+        <v>-2069772000</v>
       </c>
       <c r="G5" t="n">
-        <v>2998213000</v>
+        <v>2029825000</v>
       </c>
       <c r="H5" t="n">
-        <v>1840469000</v>
+        <v>2916103000</v>
       </c>
       <c r="I5" t="n">
-        <v>-13769000</v>
+        <v>-2439000</v>
       </c>
       <c r="J5" t="n">
-        <v>1171513000</v>
+        <v>-883839000</v>
       </c>
       <c r="K5" t="n">
-        <v>1244442000</v>
+        <v>1815025000</v>
       </c>
       <c r="L5" t="n">
-        <v>2868608000</v>
+        <v>-1045260000</v>
       </c>
       <c r="M5" t="n">
-        <v>-699344000</v>
+        <v>-595832000</v>
       </c>
       <c r="N5" t="n">
-        <v>-410676000</v>
+        <v>-311167000</v>
       </c>
       <c r="O5" t="n">
-        <v>-410676000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>-311167000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1568145000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1568145000</v>
+      </c>
       <c r="R5" t="n">
-        <v>-500480000</v>
+        <v>2215403000</v>
       </c>
       <c r="S5" t="n">
-        <v>-500480000</v>
+        <v>2215403000</v>
       </c>
       <c r="T5" t="n">
-        <v>-62999851000</v>
+        <v>-95902000000</v>
       </c>
       <c r="U5" t="n">
-        <v>62499371000</v>
+        <v>98117403000</v>
       </c>
       <c r="V5" t="n">
-        <v>-2877503000</v>
+        <v>-5296029000</v>
       </c>
       <c r="W5" t="n">
-        <v>-118638000</v>
+        <v>-7066000</v>
       </c>
       <c r="X5" t="n">
-        <v>14128000</v>
+        <v>62526000</v>
       </c>
       <c r="Y5" t="n">
-        <v>16299000</v>
+        <v>43489000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-281136000</v>
+        <v>-92147000</v>
       </c>
       <c r="AA5" t="n">
-        <v>137883000</v>
+        <v>437095000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-419019000</v>
+        <v>-529242000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-28448000</v>
+        <v>-3179555000</v>
       </c>
       <c r="AD5" t="n">
-        <v>250000</v>
+        <v>1800000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-28698000</v>
+        <v>-3181355000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-229765000</v>
+        <v>-167131000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-229765000</v>
+        <v>-167131000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2148643000</v>
+        <v>-1901738000</v>
       </c>
       <c r="AI5" t="n">
-        <v>6197000</v>
+        <v>903000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-2154840000</v>
+        <v>-1902641000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2804574000</v>
+        <v>2597165000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-198880000</v>
+        <v>-523400000</v>
       </c>
       <c r="AM5" t="n">
-        <v>915033000</v>
+        <v>-1324891000</v>
       </c>
       <c r="AN5" t="n">
-        <v>66698000</v>
+        <v>-634514000</v>
       </c>
       <c r="AO5" t="n">
-        <v>138641000</v>
+        <v>247342000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-100799000</v>
+        <v>-572908000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>910752000</v>
+        <v>-656759000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-92206000</v>
+        <v>293768000</v>
       </c>
       <c r="AS5" t="n">
-        <v>583553000</v>
+        <v>451490000</v>
       </c>
       <c r="AT5" t="n">
-        <v>39476000</v>
+        <v>18056000</v>
       </c>
       <c r="AU5" t="n">
-        <v>874493000</v>
+        <v>1348894000</v>
       </c>
       <c r="AV5" t="n">
-        <v>78874000</v>
+        <v>341983000</v>
       </c>
       <c r="AW5" t="n">
-        <v>795619000</v>
+        <v>1006911000</v>
       </c>
       <c r="AX5" t="n">
-        <v>41185000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-44653000</v>
-      </c>
+        <v>-31257000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>29814000</v>
+        <v>47387000</v>
       </c>
       <c r="BA5" t="n">
-        <v>270000</v>
+        <v>-154000</v>
       </c>
       <c r="BB5" t="n">
-        <v>281683000</v>
+        <v>2228888000</v>
       </c>
     </row>
   </sheetData>
@@ -3509,7 +3509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FJ2"/>
+  <dimension ref="A1:FM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3625,720 +3625,735 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
+          <t>compensationAsOfEpochDate</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>irWebsite</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>executiveTeam</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>maxAge</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>priceHint</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>previousClose</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dayLow</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dayHigh</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>regularMarketPreviousClose</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>regularMarketOpen</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>regularMarketDayLow</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>regularMarketDayHigh</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dividendRate</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dividendYield</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>exDividendDate</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>payoutRatio</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>fiveYearAvgDividendYield</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>pegRatio</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>targetHighPrice</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>targetLowPrice</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>targetMeanPrice</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>targetMedianPrice</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4420,7 +4435,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jiwen  Yin', 'age': 46, 'title': 'Chief Financial Officer', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Man  Ng A.C.I.S., A.C.S.', 'age': 47, 'title': 'Company Secretary', 'yearBorn': 1978, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Lei  Duan', 'age': 43, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1982, 'fiscalYear': 2025, 'totalPay': 1067232, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peiwu  Wang', 'age': 51, 'title': 'VP &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 791742, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ligang  Wang', 'age': 53, 'title': 'VP, Secretary of the Board &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 1030191, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Leyi  Wang', 'age': 53, 'title': 'Chairman &amp; President', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiwen  Yin', 'age': 46, 'title': 'Chief Financial Officer', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Man  Ng A.C.I.S., A.C.S.', 'age': 47, 'title': 'Company Secretary', 'yearBorn': 1978, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4439,488 +4454,499 @@
         <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
-      </c>
-      <c r="W2" t="inlineStr">
+        <v>1780531200</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>http://en.zhaojin.com.cn/news.php?id=223</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>86400</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>3</v>
       </c>
-      <c r="AA2" t="n">
-        <v>21.845</v>
-      </c>
       <c r="AB2" t="n">
-        <v>21.64</v>
+        <v>19.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.36</v>
+        <v>19.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>21.82</v>
+        <v>18.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>21.845</v>
+        <v>19.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>21.64</v>
+        <v>19.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>21.36</v>
+        <v>19.43</v>
       </c>
       <c r="AH2" t="n">
-        <v>21.82</v>
+        <v>18.52</v>
       </c>
       <c r="AI2" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0.11</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>0.52</v>
-      </c>
       <c r="AK2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AL2" t="n">
         <v>1780444800</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>0.052199997</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>0.74</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="AO2" t="n">
-        <v>19.45946</v>
+        <v>0.866</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.671132999999999</v>
+        <v>17.054054</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1524502</v>
+        <v>7.603319</v>
       </c>
       <c r="AR2" t="n">
-        <v>1524502</v>
+        <v>29096684</v>
       </c>
       <c r="AS2" t="n">
-        <v>19562641</v>
+        <v>29096684</v>
       </c>
       <c r="AT2" t="n">
-        <v>22296615</v>
+        <v>20430946</v>
       </c>
       <c r="AU2" t="n">
-        <v>22296615</v>
+        <v>23331351</v>
       </c>
       <c r="AV2" t="n">
-        <v>21.6</v>
+        <v>23331351</v>
       </c>
       <c r="AW2" t="n">
-        <v>21.62</v>
+        <v>18.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>18.94</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>76515688448</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>77790954759</v>
+        <v>67057504256</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.08</v>
+        <v>70033113642</v>
       </c>
       <c r="BC2" t="n">
-        <v>42.36</v>
+        <v>17.74</v>
       </c>
       <c r="BD2" t="n">
         <v>42.36</v>
       </c>
       <c r="BE2" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="BF2" t="n">
         <v>0.93</v>
       </c>
-      <c r="BF2" t="n">
-        <v>3.9289618</v>
-      </c>
       <c r="BG2" t="n">
-        <v>28.5848</v>
+        <v>3.4432986</v>
       </c>
       <c r="BH2" t="n">
-        <v>30.4575</v>
+        <v>25.7148</v>
       </c>
       <c r="BI2" t="n">
+        <v>30.2042</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>0.0045777066</v>
-      </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK2" t="n">
+        <v>0.005058169</v>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="BL2" t="b">
+      <c r="BM2" t="b">
         <v>0</v>
       </c>
-      <c r="BM2" t="n">
-        <v>89273212928</v>
-      </c>
       <c r="BN2" t="n">
+        <v>78539759616</v>
+      </c>
+      <c r="BO2" t="n">
         <v>0.21280001</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>1648133862</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>2881555597</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BR2" t="n">
         <v>0.42804</v>
       </c>
-      <c r="BR2" t="n">
-        <v>0.22474001</v>
-      </c>
       <c r="BS2" t="n">
+        <v>0.22586</v>
+      </c>
+      <c r="BT2" t="n">
         <v>3542393204</v>
       </c>
-      <c r="BT2" t="n">
-        <v>8.358309999999999</v>
-      </c>
       <c r="BU2" t="n">
-        <v>2.5842545</v>
+        <v>8.353873999999999</v>
       </c>
       <c r="BV2" t="n">
+        <v>2.2660146</v>
+      </c>
+      <c r="BW2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="BX2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="BY2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="BZ2" t="n">
         <v>0.804</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CA2" t="n">
         <v>3904820992</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CB2" t="n">
         <v>1.11</v>
       </c>
-      <c r="CB2" t="n">
-        <v>2.491024</v>
-      </c>
       <c r="CC2" t="n">
+        <v>2.4897022</v>
+      </c>
+      <c r="CD2" t="n">
         <v>0.68</v>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="CE2" t="n">
+      <c r="CF2" t="n">
         <v>1305158400</v>
       </c>
-      <c r="CF2" t="n">
-        <v>4.584</v>
-      </c>
       <c r="CG2" t="n">
-        <v>11.455</v>
+        <v>4.033</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.055769205</v>
+        <v>10.078</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.27449715</v>
+        <v>-0.033251822</v>
       </c>
       <c r="CJ2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="CK2" t="n">
         <v>0.114769</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>1780444800</v>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="CM2" t="n">
-        <v>21.6</v>
-      </c>
       <c r="CN2" t="n">
-        <v>54.03677</v>
+        <v>18.93</v>
       </c>
       <c r="CO2" t="n">
-        <v>33.710472</v>
+        <v>53.99476</v>
       </c>
       <c r="CP2" t="n">
-        <v>42.142685</v>
+        <v>33.68426</v>
       </c>
       <c r="CQ2" t="n">
-        <v>39.24264</v>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
+        <v>42.189987</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>41.32195</v>
       </c>
       <c r="CS2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>strong_buy</t>
+        </is>
+      </c>
+      <c r="CU2" t="n">
         <v>9</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CV2" t="n">
         <v>9684997120</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CW2" t="n">
         <v>2.734</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CX2" t="n">
         <v>7793083904</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CY2" t="n">
         <v>16349121536</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="CZ2" t="n">
         <v>0.635</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="DA2" t="n">
         <v>1.204</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DB2" t="n">
         <v>19474786304</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DC2" t="n">
         <v>53.811</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DD2" t="n">
         <v>5.612</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DE2" t="n">
         <v>0.06368</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DF2" t="n">
         <v>0.18235001</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DG2" t="n">
         <v>8232620032</v>
       </c>
-      <c r="DF2" t="n">
+      <c r="DH2" t="n">
         <v>2141097088</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DI2" t="n">
         <v>7356737536</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="DJ2" t="n">
         <v>0.882</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DK2" t="n">
         <v>0.467</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DL2" t="n">
         <v>0.42273</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="DM2" t="n">
         <v>0.40015998</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="DN2" t="n">
         <v>0.372</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>1818.HK</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DS2" t="b">
+      <c r="DU2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DU2" t="n">
-        <v>-1.1215333</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-8.8575</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.29081506</v>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DY2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>finmb_22546449</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-4.2488627</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1165541400000</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.8400001499999999</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>18.52 - 19.43</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
+        <v>20430946</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1.1900005</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.06708007000000001</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>17.74 - 42.36</t>
+        </is>
+      </c>
+      <c r="ER2" t="n">
+        <v>-23.43</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-0.55311614</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-3.3251822</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1777018200</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>1777018200</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1777018200</v>
+      </c>
+      <c r="EX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>2.4897022</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1.50597</v>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>ZHAOJIN MINING</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>Zhaojin Mining Industry Company Limited</t>
+        </is>
+      </c>
+      <c r="FD2" t="n">
+        <v>12.569972</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>-6.7847996</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>-0.26384804</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>-11.2742</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>-0.37326598</v>
+      </c>
+      <c r="FI2" t="n">
         <v>15</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="FJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EA2" t="b">
+      <c r="FK2" t="inlineStr">
+        <is>
+          <t>1.1 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="FL2" t="b">
         <v>0</v>
       </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_22546449</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': '1818.HK announced a cash dividend of HKD 0.115 with an ex-date of Jun. 3, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1780416000000, 'amount': '0.115'}}]</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>1780452378</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1165541400000</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.24499893</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>21.36 - 21.82</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>19562641</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>2.5200005</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>0.1320755</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>19.08 - 42.36</t>
-        </is>
-      </c>
-      <c r="EU2" t="n">
-        <v>-20.76</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>-0.49008498</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>5.5769205</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1777018200</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1777018200</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1777018200</v>
-      </c>
-      <c r="FA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>2.491024</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1.50597</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>14.342916</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>-6.9848003</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>-0.24435365</v>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>ZHAOJIN MINING</t>
-        </is>
-      </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>Zhaojin Mining Industry Company Limited</t>
-        </is>
-      </c>
-      <c r="FJ2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
